--- a/server/xlsx/血统表.xlsx
+++ b/server/xlsx/血统表.xlsx
@@ -107,8 +107,8 @@
     <t>修仙</t>
   </si>
   <si>
-    <t>普通攻击as木头撞击
-普通攻击as木桩冲撞</t>
+    <t>普通攻击as散修附带技能
+普通攻击as散修附带技能2</t>
   </si>
   <si>
     <t>剑修</t>
@@ -904,7 +904,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -923,9 +923,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -942,9 +939,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1063,7 +1057,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{0FEB2A44-7FD0-436A-936A-CE76F89FCBA9}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{F889C71E-103D-4A24-8AD5-53606E11DB83}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1393,121 +1387,121 @@
         <v>5</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:16">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:16">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" ht="69" customHeight="1" spans="1:16">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
@@ -1516,10 +1510,10 @@
       <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="12">
         <v>100</v>
       </c>
       <c r="G4">
@@ -1566,8 +1560,8 @@
       <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="14">
+      <c r="E5" s="13"/>
+      <c r="F5" s="12">
         <v>100</v>
       </c>
       <c r="G5">
@@ -1617,7 +1611,7 @@
       <c r="E6" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <v>100</v>
       </c>
       <c r="G6">
